--- a/results/Int All Data -0.5/Rando_3_permute.xlsx
+++ b/results/Int All Data -0.5/Rando_3_permute.xlsx
@@ -440,1433 +440,1433 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8213494244273909</v>
+        <v>0.8237948183203658</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8135875170627447</v>
+        <v>0.8214076311905909</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8109902177145896</v>
+        <v>0.8210915755648008</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8109195887763163</v>
+        <v>0.8204594643132206</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8064948100152545</v>
+        <v>0.8215824289398348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.806459495546118</v>
+        <v>0.8215824289398348</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8011571788459586</v>
+        <v>0.8353123041289181</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8152348749370906</v>
+        <v>0.8341875649058648</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8296868334172126</v>
+        <v>0.833345341435904</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8327079063950067</v>
+        <v>0.8406146208290772</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8360450349985911</v>
+        <v>0.8268105675088429</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8356936649036643</v>
+        <v>0.8264591974139162</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8349556102446742</v>
+        <v>0.8252656038490287</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8322152784235337</v>
+        <v>0.8279688466045937</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8323194472345044</v>
+        <v>0.8254404015982726</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7964250399816577</v>
+        <v>0.8256858282857895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7967764100765845</v>
+        <v>0.8311647173316317</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7837475004809156</v>
+        <v>0.8066165473309714</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.783150703698472</v>
+        <v>0.8130082887850474</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7788671828139563</v>
+        <v>0.8160964415082366</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.773986865146997</v>
+        <v>0.8190468855477575</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.773986865146997</v>
+        <v>0.8094592733666437</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7596584185790309</v>
+        <v>0.8058043145408302</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7647841629335073</v>
+        <v>0.7963932747053992</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7808288217176532</v>
+        <v>0.8021511303114559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7833572667239743</v>
+        <v>0.7824497381050575</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7930472731196199</v>
+        <v>0.7833961303859889</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7922403641187958</v>
+        <v>0.7877149657396412</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.79681349914216</v>
+        <v>0.7911562631541961</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7832901869785792</v>
+        <v>0.7963879509160822</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7830094458219257</v>
+        <v>0.7963879509160822</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7614152690536644</v>
+        <v>0.7937164734367756</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7635923439650589</v>
+        <v>0.787149934233456</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7792927310400342</v>
+        <v>0.7836009188150522</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7781009120715858</v>
+        <v>0.7813885294345213</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7782086300754345</v>
+        <v>0.7810724738087311</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.775960926225767</v>
+        <v>0.7813532149653848</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7770168111069862</v>
+        <v>0.7820170914932236</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7715714619338416</v>
+        <v>0.78173635033657</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.791083859619484</v>
+        <v>0.7912904226449864</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7911191740886205</v>
+        <v>0.7740803863793335</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7868674184803635</v>
+        <v>0.7743258130668504</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7870404416331682</v>
+        <v>0.7753799233516306</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7889014609187724</v>
+        <v>0.7730262760945534</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7932556107415613</v>
+        <v>0.7703954368737005</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7956781123404726</v>
+        <v>0.7650242658317072</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7956781123404726</v>
+        <v>0.7652696925192242</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7976786149061842</v>
+        <v>0.7668146561790383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8023788110345826</v>
+        <v>0.7726784551925048</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7970447290581648</v>
+        <v>0.7772373934443568</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7966580444941016</v>
+        <v>0.7772373934443568</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8137939026286032</v>
+        <v>0.770912731735676</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8179732547021481</v>
+        <v>0.7700016539238812</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.818393479138909</v>
+        <v>0.7689140037664035</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8220466633682835</v>
+        <v>0.7696502838289545</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.823801739246478</v>
+        <v>0.7687727458898572</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.823801739246478</v>
+        <v>0.7690888015156474</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8204292961737571</v>
+        <v>0.7726695822103096</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8186389058264261</v>
+        <v>0.7747778027798699</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8147702855893542</v>
+        <v>0.7828169021082916</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8166384032607145</v>
+        <v>0.7981623698954621</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8137268228832082</v>
+        <v>0.7978463142696719</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8185100701249528</v>
+        <v>0.7947192978844682</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8173500164327631</v>
+        <v>0.7966491715119065</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8182981833101335</v>
+        <v>0.7966491715119065</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8185471591905285</v>
+        <v>0.8068671203481617</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8069184061852495</v>
+        <v>0.8080642631059272</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8069184061852495</v>
+        <v>0.8118551560189697</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7971966345133453</v>
+        <v>0.8094679688891949</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7971966345133453</v>
+        <v>0.808555116480961</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7788725066032733</v>
+        <v>0.8059542679399279</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7939336840409122</v>
+        <v>0.8059542679399279</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7921079792244445</v>
+        <v>0.7938346615596148</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7946735132963413</v>
+        <v>0.7926410679947273</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8008904570011733</v>
+        <v>0.7929571236205175</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8008904570011733</v>
+        <v>0.7909195319892304</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8280359263499888</v>
+        <v>0.7814378632155261</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8280359263499888</v>
+        <v>0.763037782577864</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8359637584816837</v>
+        <v>0.7508864109212924</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.841580356211194</v>
+        <v>0.7815808956885115</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8182435257398115</v>
+        <v>0.7872363570800365</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8116363482780381</v>
+        <v>0.7890973763656407</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6605617591503516</v>
+        <v>0.7899378252391624</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6629913591350191</v>
+        <v>0.7892703995184456</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6358052515277501</v>
+        <v>0.8019143991464901</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6343291422097701</v>
+        <v>0.7936969528759465</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6395590553752171</v>
+        <v>0.7513808134892044</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6283982634509087</v>
+        <v>0.7557791507633249</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6120975304006115</v>
+        <v>0.649752159861326</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6087268619243298</v>
+        <v>0.649752159861326</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5961110783796657</v>
+        <v>0.6447305843178203</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.596072214717651</v>
+        <v>0.6422021393114992</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5993722542556597</v>
+        <v>0.6285764329333866</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5561697039476252</v>
+        <v>0.6608141067639808</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5681815923240896</v>
+        <v>0.6614462180155611</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5841220822972648</v>
+        <v>0.6311419670052834</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5774495996865353</v>
+        <v>0.6216249837624426</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5732349331438538</v>
+        <v>0.6231364075495591</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5673358196612508</v>
+        <v>0.6233818342370762</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5646308023092469</v>
+        <v>0.6233818342370762</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5822946028843581</v>
+        <v>0.6233818342370762</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.581733120571051</v>
+        <v>0.6406200865861094</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5824058700810848</v>
+        <v>0.6432915640654159</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.575837556281326</v>
+        <v>0.620606187946799</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5796690874528223</v>
+        <v>0.696742053889525</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.571098496490913</v>
+        <v>0.696742053889525</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5633719035954033</v>
+        <v>0.6756369558998588</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5788304131757397</v>
+        <v>0.6625374173659168</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5759505980744919</v>
+        <v>0.6436782486294792</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5735969508174146</v>
+        <v>0.6446264155068496</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5664318402352121</v>
+        <v>0.6390768975227343</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5453196438597898</v>
+        <v>0.6292438586541035</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.54563569948558</v>
+        <v>0.6450501891364885</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5363094853599343</v>
+        <v>0.6296165239062984</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5363094853599343</v>
+        <v>0.5981752889575382</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5238278613060604</v>
+        <v>0.5986026117800551</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5150489327222096</v>
+        <v>0.5993495394212403</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5062911218359832</v>
+        <v>0.4963998762041524</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5062911218359832</v>
+        <v>0.5021930462793456</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5075553443391438</v>
+        <v>0.5021930462793456</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5049562703945496</v>
+        <v>0.479772617409075</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5020429154206042</v>
+        <v>0.4884173865021355</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5043612482085449</v>
+        <v>0.4895085858524912</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5028109607594137</v>
+        <v>0.4739918695089549</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5028109607594137</v>
+        <v>0.4717459402557264</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5013013115687361</v>
+        <v>0.4579189946414286</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5015467382562532</v>
+        <v>0.4671763544252402</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4981778443764103</v>
+        <v>0.4729571023253602</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4956158594973917</v>
+        <v>0.4831079714162202</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4954039726825722</v>
+        <v>0.4954976713745528</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.495755342777499</v>
+        <v>0.4881559884466674</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.495755342777499</v>
+        <v>0.4883661006650478</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4984939000022005</v>
+        <v>0.5018963337547409</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5002136614112584</v>
+        <v>0.5018963337547409</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4990906967846442</v>
+        <v>0.5007027401898535</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5</v>
+        <v>0.5007027401898535</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.5007027401898535</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.5007027401898535</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5003513700949267</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.5003513700949267</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.5003513700949267</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4997192588433464</v>
+        <v>0.5000706289382731</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.5000706289382731</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1876,7 +1876,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1886,7 +1886,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1896,7 +1896,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1906,7 +1906,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
